--- a/PDR - NSGA Runs Comparison.xlsx
+++ b/PDR - NSGA Runs Comparison.xlsx
@@ -646,14 +646,15 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="7.3788228262100852E-2"/>
-          <c:y val="0.10008268574271353"/>
-          <c:w val="0.7517261672566159"/>
+          <c:x val="0.12059176688424636"/>
+          <c:y val="0.10879728269260461"/>
+          <c:w val="0.73616385968721032"/>
           <c:h val="0.72823312118664918"/>
         </c:manualLayout>
       </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -670,31 +671,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="25400" cmpd="sng">
               <a:solidFill>
                 <a:srgbClr val="00B050"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-              <a:ln w="12700" cmpd="sng">
-                <a:solidFill>
-                  <a:srgbClr val="00B050"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -772,7 +760,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-13F7-4BFF-83BF-55E094D22D4B}"/>
@@ -794,29 +781,15 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -894,7 +867,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-13F7-4BFF-83BF-55E094D22D4B}"/>
@@ -916,7 +888,10 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln w="25400" cmpd="sng">
               <a:solidFill>
                 <a:schemeClr val="accent5">
                   <a:lumMod val="60000"/>
@@ -924,31 +899,10 @@
                 </a:schemeClr>
               </a:solidFill>
               <a:prstDash val="solid"/>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="40000"/>
-                  <a:lumOff val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1026,7 +980,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-13F7-4BFF-83BF-55E094D22D4B}"/>
@@ -1048,30 +1001,16 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
               <a:prstDash val="solid"/>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1149,7 +1088,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-13F7-4BFF-83BF-55E094D22D4B}"/>
@@ -1171,30 +1109,16 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
               <a:prstDash val="solid"/>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1272,7 +1196,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-29A2-4AE6-B10D-3ADD2260AA46}"/>
@@ -1294,29 +1217,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
                 <a:srgbClr val="0066CC"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="0033CC"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="000099"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1394,7 +1305,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8A14-4645-8341-149277750544}"/>
@@ -1416,29 +1326,19 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
                 <a:srgbClr val="7D7A00"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="7D7A00"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="7D7A00"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1516,7 +1416,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-17F0-41CE-93AC-0535C7BF550C}"/>
@@ -1538,35 +1437,17 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1644,7 +1525,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-17F0-41CE-93AC-0535C7BF550C}"/>
@@ -1666,35 +1546,21 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
                 <a:schemeClr val="accent6">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1772,7 +1638,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-17F0-41CE-93AC-0535C7BF550C}"/>
@@ -1794,29 +1659,19 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="25400">
               <a:solidFill>
                 <a:schemeClr val="accent6"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$C$1:$L$1</c:f>
@@ -1894,7 +1749,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-17F0-41CE-93AC-0535C7BF550C}"/>
@@ -1909,22 +1763,21 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
+        <c:gapWidth val="150"/>
         <c:axId val="1616784224"/>
         <c:axId val="1616788800"/>
-      </c:lineChart>
+      </c:barChart>
       <c:catAx>
         <c:axId val="1616784224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="t" anchorCtr="0"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1959,8 +1812,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.2455724990299078"/>
-              <c:y val="0.91511021906575407"/>
+              <c:x val="1.0494445770036311E-2"/>
+              <c:y val="9.4422772316859069E-2"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1972,7 +1825,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="t" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2043,7 +1896,7 @@
           <c:min val="45"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2061,7 +1914,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -2100,8 +1953,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="1.6980662988268756E-2"/>
-              <c:y val="0.39739420730303443"/>
+              <c:x val="0.37327086180343161"/>
+              <c:y val="0.91155553268259759"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2113,7 +1966,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2184,10 +2037,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.83462108558744208"/>
-          <c:y val="9.8975634581624991E-2"/>
-          <c:w val="8.7829957894381652E-2"/>
-          <c:h val="0.72217704813042161"/>
+          <c:x val="0.8701019320328427"/>
+          <c:y val="0.11640482848140714"/>
+          <c:w val="8.4963061327547829E-2"/>
+          <c:h val="0.6030775564819103"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -2804,13 +2657,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>9526</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>276226</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>85724</xdr:rowOff>
     </xdr:to>
